--- a/exemple-ePrescription/ig/observations-summary.xlsx
+++ b/exemple-ePrescription/ig/observations-summary.xlsx
@@ -230,7 +230,7 @@
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-signe-vital-cisis (required)</t>
   </si>
   <si>
-    <t>fr-Observation-vital-signs-panel-document</t>
+    <t>fr-observation-vital-signs-panel-document</t>
   </si>
   <si>
     <t>Observation - FR Observation Vital Signs Panel Document</t>
